--- a/data/base/Backlog_7.xlsx
+++ b/data/base/Backlog_7.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A4CFA52-290F-4632-AA46-0B260C8B8E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DE6DA5-BC7E-4486-8CF5-21474485916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="1" r:id="rId1"/>
     <sheet name="ITI" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -260,6 +260,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,7 +642,7 @@
       <c r="C2" s="12">
         <v>2026</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="14">
         <v>7</v>
       </c>
       <c r="E2" s="10">
@@ -645,7 +651,7 @@
       <c r="F2" s="10">
         <v>46080</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="15">
         <v>8913</v>
       </c>
       <c r="H2" s="11">
@@ -671,7 +677,7 @@
       <c r="C3" s="12">
         <v>2026</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="14">
         <v>7</v>
       </c>
       <c r="E3" s="10">
@@ -680,7 +686,7 @@
       <c r="F3" s="10">
         <v>46080</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="15">
         <v>10448</v>
       </c>
       <c r="H3" s="11">
@@ -706,7 +712,7 @@
       <c r="C4" s="12">
         <v>2026</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="14">
         <v>7</v>
       </c>
       <c r="E4" s="10">
@@ -715,7 +721,7 @@
       <c r="F4" s="10">
         <v>46080</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>10613</v>
       </c>
       <c r="H4" s="11">
@@ -741,7 +747,7 @@
       <c r="C5" s="12">
         <v>2026</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="14">
         <v>7</v>
       </c>
       <c r="E5" s="10">
@@ -750,7 +756,7 @@
       <c r="F5" s="10">
         <v>46080</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>10758</v>
       </c>
       <c r="H5" s="11">
@@ -776,7 +782,7 @@
       <c r="C6" s="12">
         <v>2026</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="14">
         <v>7</v>
       </c>
       <c r="E6" s="10">
@@ -785,7 +791,7 @@
       <c r="F6" s="10">
         <v>46080</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>11185</v>
       </c>
       <c r="H6" s="11">
@@ -811,7 +817,7 @@
       <c r="C7" s="12">
         <v>2026</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="14">
         <v>7</v>
       </c>
       <c r="E7" s="10">
@@ -820,7 +826,7 @@
       <c r="F7" s="10">
         <v>46080</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>11259</v>
       </c>
       <c r="H7" s="11">
@@ -846,7 +852,7 @@
       <c r="C8" s="12">
         <v>2026</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="14">
         <v>7</v>
       </c>
       <c r="E8" s="10">
@@ -855,7 +861,7 @@
       <c r="F8" s="10">
         <v>46080</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <v>11308</v>
       </c>
       <c r="H8" s="11">
@@ -901,7 +907,7 @@
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="4" bestFit="1" customWidth="1"/>
@@ -954,12 +960,12 @@
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="9">
         <v>2026</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="14">
         <v>7</v>
       </c>
       <c r="E2" s="10">
@@ -968,11 +974,11 @@
       <c r="F2" s="10">
         <v>46080</v>
       </c>
-      <c r="G2" s="12">
-        <v>7400</v>
+      <c r="G2" s="15">
+        <v>10664</v>
       </c>
       <c r="H2" s="11">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="I2" s="10">
         <v>46076</v>
@@ -989,12 +995,12 @@
         <v>4</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="9">
         <v>2026</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="14">
         <v>7</v>
       </c>
       <c r="E3" s="10">
@@ -1003,11 +1009,11 @@
       <c r="F3" s="10">
         <v>46080</v>
       </c>
-      <c r="G3" s="12">
-        <v>9411</v>
+      <c r="G3" s="15">
+        <v>11252</v>
       </c>
       <c r="H3" s="11">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I3" s="10">
         <v>46076</v>
@@ -1024,12 +1030,12 @@
         <v>4</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="9">
         <v>2026</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="14">
         <v>7</v>
       </c>
       <c r="E4" s="10">
@@ -1038,11 +1044,11 @@
       <c r="F4" s="10">
         <v>46080</v>
       </c>
-      <c r="G4" s="12">
-        <v>9790</v>
+      <c r="G4" s="15">
+        <v>7400</v>
       </c>
       <c r="H4" s="11">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I4" s="10">
         <v>46076</v>
@@ -1059,12 +1065,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9">
         <v>2026</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="14">
         <v>7</v>
       </c>
       <c r="E5" s="10">
@@ -1073,11 +1079,11 @@
       <c r="F5" s="10">
         <v>46080</v>
       </c>
-      <c r="G5" s="12">
-        <v>9978</v>
+      <c r="G5" s="15">
+        <v>9411</v>
       </c>
       <c r="H5" s="11">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I5" s="10">
         <v>46076</v>
@@ -1099,7 +1105,7 @@
       <c r="C6" s="9">
         <v>2026</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="14">
         <v>7</v>
       </c>
       <c r="E6" s="10">
@@ -1108,7 +1114,7 @@
       <c r="F6" s="10">
         <v>46080</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>10016</v>
       </c>
       <c r="H6" s="11">
@@ -1134,7 +1140,7 @@
       <c r="C7" s="9">
         <v>2026</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="14">
         <v>7</v>
       </c>
       <c r="E7" s="10">
@@ -1143,7 +1149,7 @@
       <c r="F7" s="10">
         <v>46080</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>10164</v>
       </c>
       <c r="H7" s="11">
@@ -1164,12 +1170,12 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9">
         <v>2026</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="14">
         <v>7</v>
       </c>
       <c r="E8" s="10">
@@ -1178,8 +1184,8 @@
       <c r="F8" s="10">
         <v>46080</v>
       </c>
-      <c r="G8" s="12">
-        <v>10204</v>
+      <c r="G8" s="15">
+        <v>10980</v>
       </c>
       <c r="H8" s="11">
         <v>46054</v>
@@ -1199,12 +1205,12 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" s="9">
         <v>2026</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="14">
         <v>7</v>
       </c>
       <c r="E9" s="10">
@@ -1213,8 +1219,8 @@
       <c r="F9" s="10">
         <v>46080</v>
       </c>
-      <c r="G9" s="12">
-        <v>10233</v>
+      <c r="G9" s="15">
+        <v>10733</v>
       </c>
       <c r="H9" s="11">
         <v>46054</v>
@@ -1234,12 +1240,12 @@
         <v>4</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9">
         <v>2026</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="14">
         <v>7</v>
       </c>
       <c r="E10" s="10">
@@ -1248,11 +1254,11 @@
       <c r="F10" s="10">
         <v>46080</v>
       </c>
-      <c r="G10" s="12">
-        <v>10470</v>
+      <c r="G10" s="15">
+        <v>9790</v>
       </c>
       <c r="H10" s="11">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I10" s="10">
         <v>46076</v>
@@ -1269,12 +1275,12 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="9">
         <v>2026</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="14">
         <v>7</v>
       </c>
       <c r="E11" s="10">
@@ -1283,8 +1289,8 @@
       <c r="F11" s="10">
         <v>46080</v>
       </c>
-      <c r="G11" s="12">
-        <v>10664</v>
+      <c r="G11" s="15">
+        <v>10233</v>
       </c>
       <c r="H11" s="11">
         <v>46054</v>
@@ -1304,12 +1310,12 @@
         <v>4</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="9">
         <v>2026</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="14">
         <v>7</v>
       </c>
       <c r="E12" s="10">
@@ -1318,8 +1324,8 @@
       <c r="F12" s="10">
         <v>46080</v>
       </c>
-      <c r="G12" s="12">
-        <v>10733</v>
+      <c r="G12" s="15">
+        <v>10870</v>
       </c>
       <c r="H12" s="11">
         <v>46054</v>
@@ -1339,12 +1345,12 @@
         <v>4</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C13" s="9">
         <v>2026</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="14">
         <v>7</v>
       </c>
       <c r="E13" s="10">
@@ -1353,8 +1359,8 @@
       <c r="F13" s="10">
         <v>46080</v>
       </c>
-      <c r="G13" s="12">
-        <v>10797</v>
+      <c r="G13" s="15">
+        <v>11313</v>
       </c>
       <c r="H13" s="11">
         <v>46054</v>
@@ -1374,12 +1380,12 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C14" s="9">
         <v>2026</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="14">
         <v>7</v>
       </c>
       <c r="E14" s="10">
@@ -1388,8 +1394,8 @@
       <c r="F14" s="10">
         <v>46080</v>
       </c>
-      <c r="G14" s="12">
-        <v>10870</v>
+      <c r="G14" s="15">
+        <v>10470</v>
       </c>
       <c r="H14" s="11">
         <v>46054</v>
@@ -1414,7 +1420,7 @@
       <c r="C15" s="9">
         <v>2026</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="14">
         <v>7</v>
       </c>
       <c r="E15" s="10">
@@ -1423,7 +1429,7 @@
       <c r="F15" s="10">
         <v>46080</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="15">
         <v>10955</v>
       </c>
       <c r="H15" s="11">
@@ -1444,12 +1450,12 @@
         <v>4</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C16" s="9">
         <v>2026</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="14">
         <v>7</v>
       </c>
       <c r="E16" s="10">
@@ -1458,8 +1464,8 @@
       <c r="F16" s="10">
         <v>46080</v>
       </c>
-      <c r="G16" s="12">
-        <v>10980</v>
+      <c r="G16" s="15">
+        <v>10986</v>
       </c>
       <c r="H16" s="11">
         <v>46054</v>
@@ -1479,12 +1485,12 @@
         <v>4</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="9">
         <v>2026</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="10">
@@ -1493,8 +1499,8 @@
       <c r="F17" s="10">
         <v>46080</v>
       </c>
-      <c r="G17" s="12">
-        <v>10986</v>
+      <c r="G17" s="15">
+        <v>11268</v>
       </c>
       <c r="H17" s="11">
         <v>46054</v>
@@ -1514,12 +1520,12 @@
         <v>4</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9">
         <v>2026</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="14">
         <v>7</v>
       </c>
       <c r="E18" s="10">
@@ -1528,8 +1534,8 @@
       <c r="F18" s="10">
         <v>46080</v>
       </c>
-      <c r="G18" s="12">
-        <v>11110</v>
+      <c r="G18" s="15">
+        <v>11286</v>
       </c>
       <c r="H18" s="11">
         <v>46054</v>
@@ -1549,12 +1555,12 @@
         <v>4</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19" s="9">
         <v>2026</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="10">
@@ -1563,8 +1569,8 @@
       <c r="F19" s="10">
         <v>46080</v>
       </c>
-      <c r="G19" s="12">
-        <v>11252</v>
+      <c r="G19" s="15">
+        <v>10204</v>
       </c>
       <c r="H19" s="11">
         <v>46054</v>
@@ -1584,12 +1590,12 @@
         <v>4</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C20" s="9">
         <v>2026</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="10">
@@ -1598,8 +1604,8 @@
       <c r="F20" s="10">
         <v>46080</v>
       </c>
-      <c r="G20" s="12">
-        <v>11268</v>
+      <c r="G20" s="15">
+        <v>11287</v>
       </c>
       <c r="H20" s="11">
         <v>46054</v>
@@ -1619,12 +1625,12 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C21" s="9">
         <v>2026</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="14">
         <v>7</v>
       </c>
       <c r="E21" s="10">
@@ -1633,8 +1639,8 @@
       <c r="F21" s="10">
         <v>46080</v>
       </c>
-      <c r="G21" s="12">
-        <v>11286</v>
+      <c r="G21" s="15">
+        <v>9978</v>
       </c>
       <c r="H21" s="11">
         <v>46054</v>
@@ -1654,12 +1660,12 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C22" s="9">
         <v>2026</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="14">
         <v>7</v>
       </c>
       <c r="E22" s="10">
@@ -1668,8 +1674,8 @@
       <c r="F22" s="10">
         <v>46080</v>
       </c>
-      <c r="G22" s="12">
-        <v>11287</v>
+      <c r="G22" s="15">
+        <v>10797</v>
       </c>
       <c r="H22" s="11">
         <v>46054</v>
@@ -1689,12 +1695,12 @@
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23" s="9">
         <v>2026</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="14">
         <v>7</v>
       </c>
       <c r="E23" s="10">
@@ -1703,8 +1709,8 @@
       <c r="F23" s="10">
         <v>46080</v>
       </c>
-      <c r="G23" s="12">
-        <v>11310</v>
+      <c r="G23" s="15">
+        <v>11110</v>
       </c>
       <c r="H23" s="11">
         <v>46054</v>
@@ -1724,12 +1730,12 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C24" s="9">
         <v>2026</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="14">
         <v>7</v>
       </c>
       <c r="E24" s="10">
@@ -1738,8 +1744,8 @@
       <c r="F24" s="10">
         <v>46080</v>
       </c>
-      <c r="G24" s="12">
-        <v>11313</v>
+      <c r="G24" s="15">
+        <v>11310</v>
       </c>
       <c r="H24" s="11">
         <v>46054</v>
@@ -1764,7 +1770,7 @@
       <c r="C25" s="9">
         <v>2026</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="10">
@@ -1773,7 +1779,7 @@
       <c r="F25" s="10">
         <v>46080</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="15">
         <v>11338</v>
       </c>
       <c r="H25" s="11">
@@ -1835,9 +1841,9 @@
       <c r="I36" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
-      <sortCondition ref="B1:B15"/>
+  <autoFilter ref="A1:K25" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
+      <sortCondition ref="B1:B25"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/base/Backlog_7.xlsx
+++ b/data/base/Backlog_7.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DE6DA5-BC7E-4486-8CF5-21474485916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A88C111-091B-46EB-ACBC-A5AF651F2734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="1" r:id="rId1"/>
     <sheet name="ITI" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="30">
   <si>
     <t>Backlog</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Arthur Hassuma</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -227,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -260,12 +263,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,12 +634,12 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" s="12">
         <v>2026</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>7</v>
       </c>
       <c r="E2" s="10">
@@ -651,8 +648,8 @@
       <c r="F2" s="10">
         <v>46080</v>
       </c>
-      <c r="G2" s="15">
-        <v>8913</v>
+      <c r="G2" s="12">
+        <v>10758</v>
       </c>
       <c r="H2" s="11">
         <v>46054</v>
@@ -661,7 +658,7 @@
         <v>46076</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K2" s="12" t="s">
         <v>15</v>
@@ -672,12 +669,12 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C3" s="12">
         <v>2026</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="9">
         <v>7</v>
       </c>
       <c r="E3" s="10">
@@ -686,8 +683,8 @@
       <c r="F3" s="10">
         <v>46080</v>
       </c>
-      <c r="G3" s="15">
-        <v>10448</v>
+      <c r="G3" s="12">
+        <v>11185</v>
       </c>
       <c r="H3" s="11">
         <v>46054</v>
@@ -707,12 +704,12 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="12">
         <v>2026</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>7</v>
       </c>
       <c r="E4" s="10">
@@ -721,8 +718,8 @@
       <c r="F4" s="10">
         <v>46080</v>
       </c>
-      <c r="G4" s="15">
-        <v>10613</v>
+      <c r="G4" s="12">
+        <v>11308</v>
       </c>
       <c r="H4" s="11">
         <v>46054</v>
@@ -731,7 +728,7 @@
         <v>46076</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>15</v>
@@ -742,12 +739,12 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" s="12">
         <v>2026</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>7</v>
       </c>
       <c r="E5" s="10">
@@ -756,8 +753,8 @@
       <c r="F5" s="10">
         <v>46080</v>
       </c>
-      <c r="G5" s="15">
-        <v>10758</v>
+      <c r="G5" s="12">
+        <v>8913</v>
       </c>
       <c r="H5" s="11">
         <v>46054</v>
@@ -766,7 +763,7 @@
         <v>46076</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>15</v>
@@ -777,12 +774,12 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" s="12">
         <v>2026</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>7</v>
       </c>
       <c r="E6" s="10">
@@ -791,8 +788,8 @@
       <c r="F6" s="10">
         <v>46080</v>
       </c>
-      <c r="G6" s="15">
-        <v>11185</v>
+      <c r="G6" s="12">
+        <v>10448</v>
       </c>
       <c r="H6" s="11">
         <v>46054</v>
@@ -801,7 +798,7 @@
         <v>46076</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>15</v>
@@ -817,7 +814,7 @@
       <c r="C7" s="12">
         <v>2026</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>7</v>
       </c>
       <c r="E7" s="10">
@@ -826,8 +823,8 @@
       <c r="F7" s="10">
         <v>46080</v>
       </c>
-      <c r="G7" s="15">
-        <v>11259</v>
+      <c r="G7" s="12">
+        <v>10613</v>
       </c>
       <c r="H7" s="11">
         <v>46054</v>
@@ -836,7 +833,7 @@
         <v>46076</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>15</v>
@@ -847,12 +844,12 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" s="12">
         <v>2026</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="9">
         <v>7</v>
       </c>
       <c r="E8" s="10">
@@ -861,8 +858,8 @@
       <c r="F8" s="10">
         <v>46080</v>
       </c>
-      <c r="G8" s="15">
-        <v>11308</v>
+      <c r="G8" s="12">
+        <v>11259</v>
       </c>
       <c r="H8" s="11">
         <v>46054</v>
@@ -871,7 +868,7 @@
         <v>46076</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>15</v>
@@ -907,7 +904,7 @@
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="4" bestFit="1" customWidth="1"/>
@@ -965,7 +962,7 @@
       <c r="C2" s="9">
         <v>2026</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>7</v>
       </c>
       <c r="E2" s="10">
@@ -974,7 +971,7 @@
       <c r="F2" s="10">
         <v>46080</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="12">
         <v>10664</v>
       </c>
       <c r="H2" s="11">
@@ -1000,7 +997,7 @@
       <c r="C3" s="9">
         <v>2026</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="9">
         <v>7</v>
       </c>
       <c r="E3" s="10">
@@ -1009,7 +1006,7 @@
       <c r="F3" s="10">
         <v>46080</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="12">
         <v>11252</v>
       </c>
       <c r="H3" s="11">
@@ -1019,7 +1016,7 @@
         <v>46076</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>11</v>
@@ -1035,7 +1032,7 @@
       <c r="C4" s="9">
         <v>2026</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>7</v>
       </c>
       <c r="E4" s="10">
@@ -1044,7 +1041,7 @@
       <c r="F4" s="10">
         <v>46080</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="12">
         <v>7400</v>
       </c>
       <c r="H4" s="11">
@@ -1070,7 +1067,7 @@
       <c r="C5" s="9">
         <v>2026</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>7</v>
       </c>
       <c r="E5" s="10">
@@ -1079,7 +1076,7 @@
       <c r="F5" s="10">
         <v>46080</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="12">
         <v>9411</v>
       </c>
       <c r="H5" s="11">
@@ -1105,7 +1102,7 @@
       <c r="C6" s="9">
         <v>2026</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>7</v>
       </c>
       <c r="E6" s="10">
@@ -1114,7 +1111,7 @@
       <c r="F6" s="10">
         <v>46080</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="12">
         <v>10016</v>
       </c>
       <c r="H6" s="11">
@@ -1140,7 +1137,7 @@
       <c r="C7" s="9">
         <v>2026</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>7</v>
       </c>
       <c r="E7" s="10">
@@ -1149,7 +1146,7 @@
       <c r="F7" s="10">
         <v>46080</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="12">
         <v>10164</v>
       </c>
       <c r="H7" s="11">
@@ -1175,7 +1172,7 @@
       <c r="C8" s="9">
         <v>2026</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="9">
         <v>7</v>
       </c>
       <c r="E8" s="10">
@@ -1184,7 +1181,7 @@
       <c r="F8" s="10">
         <v>46080</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>10980</v>
       </c>
       <c r="H8" s="11">
@@ -1194,7 +1191,7 @@
         <v>46076</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>11</v>
@@ -1210,7 +1207,7 @@
       <c r="C9" s="9">
         <v>2026</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="10">
@@ -1219,7 +1216,7 @@
       <c r="F9" s="10">
         <v>46080</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="12">
         <v>10733</v>
       </c>
       <c r="H9" s="11">
@@ -1229,7 +1226,7 @@
         <v>46076</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>11</v>
@@ -1245,7 +1242,7 @@
       <c r="C10" s="9">
         <v>2026</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="9">
         <v>7</v>
       </c>
       <c r="E10" s="10">
@@ -1254,7 +1251,7 @@
       <c r="F10" s="10">
         <v>46080</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="12">
         <v>9790</v>
       </c>
       <c r="H10" s="11">
@@ -1264,7 +1261,7 @@
         <v>46076</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>11</v>
@@ -1280,7 +1277,7 @@
       <c r="C11" s="9">
         <v>2026</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="9">
         <v>7</v>
       </c>
       <c r="E11" s="10">
@@ -1289,7 +1286,7 @@
       <c r="F11" s="10">
         <v>46080</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="12">
         <v>10233</v>
       </c>
       <c r="H11" s="11">
@@ -1315,7 +1312,7 @@
       <c r="C12" s="9">
         <v>2026</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="9">
         <v>7</v>
       </c>
       <c r="E12" s="10">
@@ -1324,7 +1321,7 @@
       <c r="F12" s="10">
         <v>46080</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="12">
         <v>10870</v>
       </c>
       <c r="H12" s="11">
@@ -1334,7 +1331,7 @@
         <v>46076</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>11</v>
@@ -1350,7 +1347,7 @@
       <c r="C13" s="9">
         <v>2026</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="9">
         <v>7</v>
       </c>
       <c r="E13" s="10">
@@ -1359,7 +1356,7 @@
       <c r="F13" s="10">
         <v>46080</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="12">
         <v>11313</v>
       </c>
       <c r="H13" s="11">
@@ -1369,7 +1366,7 @@
         <v>46076</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1385,7 +1382,7 @@
       <c r="C14" s="9">
         <v>2026</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="9">
         <v>7</v>
       </c>
       <c r="E14" s="10">
@@ -1394,7 +1391,7 @@
       <c r="F14" s="10">
         <v>46080</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="12">
         <v>10470</v>
       </c>
       <c r="H14" s="11">
@@ -1404,7 +1401,7 @@
         <v>46076</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
@@ -1420,7 +1417,7 @@
       <c r="C15" s="9">
         <v>2026</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="9">
         <v>7</v>
       </c>
       <c r="E15" s="10">
@@ -1429,7 +1426,7 @@
       <c r="F15" s="10">
         <v>46080</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="12">
         <v>10955</v>
       </c>
       <c r="H15" s="11">
@@ -1439,7 +1436,7 @@
         <v>46076</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>11</v>
@@ -1455,7 +1452,7 @@
       <c r="C16" s="9">
         <v>2026</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="9">
         <v>7</v>
       </c>
       <c r="E16" s="10">
@@ -1464,7 +1461,7 @@
       <c r="F16" s="10">
         <v>46080</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="12">
         <v>10986</v>
       </c>
       <c r="H16" s="11">
@@ -1474,7 +1471,7 @@
         <v>46076</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1490,7 +1487,7 @@
       <c r="C17" s="9">
         <v>2026</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="9">
         <v>7</v>
       </c>
       <c r="E17" s="10">
@@ -1499,7 +1496,7 @@
       <c r="F17" s="10">
         <v>46080</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="12">
         <v>11268</v>
       </c>
       <c r="H17" s="11">
@@ -1525,7 +1522,7 @@
       <c r="C18" s="9">
         <v>2026</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="9">
         <v>7</v>
       </c>
       <c r="E18" s="10">
@@ -1534,7 +1531,7 @@
       <c r="F18" s="10">
         <v>46080</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="12">
         <v>11286</v>
       </c>
       <c r="H18" s="11">
@@ -1560,7 +1557,7 @@
       <c r="C19" s="9">
         <v>2026</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="9">
         <v>7</v>
       </c>
       <c r="E19" s="10">
@@ -1569,7 +1566,7 @@
       <c r="F19" s="10">
         <v>46080</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="12">
         <v>10204</v>
       </c>
       <c r="H19" s="11">
@@ -1579,7 +1576,7 @@
         <v>46076</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
@@ -1595,7 +1592,7 @@
       <c r="C20" s="9">
         <v>2026</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="9">
         <v>7</v>
       </c>
       <c r="E20" s="10">
@@ -1604,7 +1601,7 @@
       <c r="F20" s="10">
         <v>46080</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="12">
         <v>11287</v>
       </c>
       <c r="H20" s="11">
@@ -1614,7 +1611,7 @@
         <v>46076</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>11</v>
@@ -1630,7 +1627,7 @@
       <c r="C21" s="9">
         <v>2026</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="9">
         <v>7</v>
       </c>
       <c r="E21" s="10">
@@ -1639,7 +1636,7 @@
       <c r="F21" s="10">
         <v>46080</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="12">
         <v>9978</v>
       </c>
       <c r="H21" s="11">
@@ -1665,7 +1662,7 @@
       <c r="C22" s="9">
         <v>2026</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="9">
         <v>7</v>
       </c>
       <c r="E22" s="10">
@@ -1674,7 +1671,7 @@
       <c r="F22" s="10">
         <v>46080</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="12">
         <v>10797</v>
       </c>
       <c r="H22" s="11">
@@ -1684,7 +1681,7 @@
         <v>46076</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>11</v>
@@ -1700,7 +1697,7 @@
       <c r="C23" s="9">
         <v>2026</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="9">
         <v>7</v>
       </c>
       <c r="E23" s="10">
@@ -1709,7 +1706,7 @@
       <c r="F23" s="10">
         <v>46080</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="12">
         <v>11110</v>
       </c>
       <c r="H23" s="11">
@@ -1719,7 +1716,7 @@
         <v>46076</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>11</v>
@@ -1735,7 +1732,7 @@
       <c r="C24" s="9">
         <v>2026</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="9">
         <v>7</v>
       </c>
       <c r="E24" s="10">
@@ -1744,7 +1741,7 @@
       <c r="F24" s="10">
         <v>46080</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="12">
         <v>11310</v>
       </c>
       <c r="H24" s="11">
@@ -1754,7 +1751,7 @@
         <v>46076</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>11</v>
@@ -1770,7 +1767,7 @@
       <c r="C25" s="9">
         <v>2026</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="9">
         <v>7</v>
       </c>
       <c r="E25" s="10">
@@ -1779,7 +1776,7 @@
       <c r="F25" s="10">
         <v>46080</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="12">
         <v>11338</v>
       </c>
       <c r="H25" s="11">
@@ -1841,9 +1838,9 @@
       <c r="I36" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+  <autoFilter ref="A1:K15" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
-      <sortCondition ref="B1:B25"/>
+      <sortCondition ref="B1:B15"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
